--- a/Team-Data/2008-09/2-25-2008-09.xlsx
+++ b/Team-Data/2008-09/2-25-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,55 +728,55 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E2" t="n">
         <v>32</v>
       </c>
       <c r="F2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
       </c>
       <c r="I2" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J2" t="n">
         <v>78.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.456</v>
       </c>
       <c r="L2" t="n">
         <v>7.6</v>
       </c>
       <c r="M2" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P2" t="n">
         <v>26</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.736</v>
+        <v>0.732</v>
       </c>
       <c r="R2" t="n">
         <v>10.6</v>
       </c>
       <c r="S2" t="n">
-        <v>29.3</v>
+        <v>29.4</v>
       </c>
       <c r="T2" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U2" t="n">
         <v>20.8</v>
@@ -727,40 +794,40 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA2" t="n">
         <v>20.9</v>
       </c>
       <c r="AB2" t="n">
-        <v>98.7</v>
+        <v>98.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
         <v>12</v>
       </c>
       <c r="AF2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
         <v>29</v>
       </c>
       <c r="AI2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ2" t="n">
         <v>23</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
@@ -769,7 +836,7 @@
         <v>5</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO2" t="n">
         <v>18</v>
@@ -784,22 +851,22 @@
         <v>22</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU2" t="n">
         <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AW2" t="n">
         <v>9</v>
       </c>
       <c r="AX2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -811,7 +878,7 @@
         <v>18</v>
       </c>
       <c r="BB2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC2" t="n">
         <v>13</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -846,13 +913,13 @@
         <v>58</v>
       </c>
       <c r="E3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>0.776</v>
+        <v>0.793</v>
       </c>
       <c r="H3" t="n">
         <v>48.4</v>
@@ -861,67 +928,67 @@
         <v>37.5</v>
       </c>
       <c r="J3" t="n">
-        <v>77.2</v>
+        <v>77.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.486</v>
+        <v>0.485</v>
       </c>
       <c r="L3" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M3" t="n">
         <v>16.7</v>
       </c>
       <c r="N3" t="n">
-        <v>0.393</v>
+        <v>0.389</v>
       </c>
       <c r="O3" t="n">
         <v>20.2</v>
       </c>
       <c r="P3" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="W3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y3" t="n">
         <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AB3" t="n">
         <v>101.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE3" t="n">
         <v>2</v>
@@ -945,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM3" t="n">
         <v>19</v>
@@ -969,7 +1036,7 @@
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU3" t="n">
         <v>3</v>
@@ -978,10 +1045,10 @@
         <v>27</v>
       </c>
       <c r="AW3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AY3" t="n">
         <v>13</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
         <v>35</v>
       </c>
       <c r="G4" t="n">
-        <v>0.397</v>
+        <v>0.386</v>
       </c>
       <c r="H4" t="n">
         <v>48.7</v>
@@ -1046,7 +1113,7 @@
         <v>76.59999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
         <v>5.8</v>
@@ -1055,13 +1122,13 @@
         <v>15.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.366</v>
+        <v>0.363</v>
       </c>
       <c r="O4" t="n">
         <v>17.9</v>
       </c>
       <c r="P4" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q4" t="n">
         <v>0.738</v>
@@ -1073,16 +1140,16 @@
         <v>28.7</v>
       </c>
       <c r="T4" t="n">
-        <v>39.4</v>
+        <v>39.5</v>
       </c>
       <c r="U4" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="V4" t="n">
         <v>15.6</v>
       </c>
       <c r="W4" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
         <v>4.8</v>
@@ -1091,28 +1158,28 @@
         <v>6.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="AA4" t="n">
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>92.3</v>
+        <v>92.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>-2.1</v>
+        <v>-2.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
         <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
         <v>2</v>
@@ -1133,13 +1200,13 @@
         <v>23</v>
       </c>
       <c r="AN4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP4" t="n">
         <v>18</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>20</v>
       </c>
       <c r="AQ4" t="n">
         <v>28</v>
@@ -1163,7 +1230,7 @@
         <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -1210,13 +1277,13 @@
         <v>57</v>
       </c>
       <c r="E5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G5" t="n">
-        <v>0.439</v>
+        <v>0.456</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
@@ -1225,10 +1292,10 @@
         <v>37.8</v>
       </c>
       <c r="J5" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L5" t="n">
         <v>5.9</v>
@@ -1237,34 +1304,34 @@
         <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>24.3</v>
+        <v>24.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.793</v>
+        <v>0.791</v>
       </c>
       <c r="R5" t="n">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="S5" t="n">
         <v>30.4</v>
       </c>
       <c r="T5" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U5" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X5" t="n">
         <v>5.6</v>
@@ -1273,28 +1340,28 @@
         <v>5.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>100.8</v>
+        <v>100.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.5</v>
+        <v>-1</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG5" t="n">
         <v>18</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>19</v>
       </c>
       <c r="AH5" t="n">
         <v>3</v>
@@ -1306,7 +1373,7 @@
         <v>6</v>
       </c>
       <c r="AK5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
         <v>22</v>
@@ -1315,7 +1382,7 @@
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO5" t="n">
         <v>12</v>
@@ -1324,13 +1391,13 @@
         <v>17</v>
       </c>
       <c r="AQ5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR5" t="n">
         <v>7</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
         <v>10</v>
@@ -1339,28 +1406,28 @@
         <v>12</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AW5" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BA5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BB5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BC5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -1389,46 +1456,46 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" t="n">
         <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.8</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.2</v>
+        <v>37</v>
       </c>
       <c r="J6" t="n">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K6" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L6" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.389</v>
+        <v>0.386</v>
       </c>
       <c r="O6" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P6" t="n">
-        <v>24.7</v>
+        <v>24.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R6" t="n">
         <v>10.7</v>
@@ -1440,40 +1507,40 @@
         <v>41.8</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>12.9</v>
+        <v>13.1</v>
       </c>
       <c r="W6" t="n">
         <v>7.5</v>
       </c>
       <c r="X6" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.1</v>
+        <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>10.2</v>
       </c>
       <c r="AD6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
         <v>2</v>
@@ -1482,10 +1549,10 @@
         <v>26</v>
       </c>
       <c r="AI6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AK6" t="n">
         <v>5</v>
@@ -1497,19 +1564,19 @@
         <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO6" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>22</v>
       </c>
       <c r="AR6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
         <v>10</v>
@@ -1518,28 +1585,28 @@
         <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX6" t="n">
         <v>5</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>4</v>
       </c>
       <c r="AY6" t="n">
         <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E7" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F7" t="n">
         <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>0.596</v>
+        <v>0.589</v>
       </c>
       <c r="H7" t="n">
         <v>48.4</v>
@@ -1589,49 +1656,49 @@
         <v>38.1</v>
       </c>
       <c r="J7" t="n">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L7" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M7" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N7" t="n">
-        <v>0.35</v>
+        <v>0.348</v>
       </c>
       <c r="O7" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="P7" t="n">
-        <v>22</v>
+        <v>21.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T7" t="n">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="U7" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="V7" t="n">
-        <v>13.5</v>
+        <v>13.3</v>
       </c>
       <c r="W7" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X7" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Y7" t="n">
         <v>4.1</v>
@@ -1640,16 +1707,16 @@
         <v>19.1</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>100.9</v>
+        <v>100.6</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AD7" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>11</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI7" t="n">
         <v>7</v>
@@ -1679,10 +1746,10 @@
         <v>11</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1694,16 +1761,16 @@
         <v>14</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AT7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1718,10 +1785,10 @@
         <v>3</v>
       </c>
       <c r="BA7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BB7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -1753,37 +1820,37 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F8" t="n">
         <v>20</v>
       </c>
       <c r="G8" t="n">
-        <v>0.655</v>
+        <v>0.649</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>36.9</v>
+        <v>36.8</v>
       </c>
       <c r="J8" t="n">
         <v>78.3</v>
       </c>
       <c r="K8" t="n">
-        <v>0.471</v>
+        <v>0.47</v>
       </c>
       <c r="L8" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="N8" t="n">
-        <v>0.367</v>
+        <v>0.364</v>
       </c>
       <c r="O8" t="n">
         <v>23.1</v>
@@ -1795,10 +1862,10 @@
         <v>0.756</v>
       </c>
       <c r="R8" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T8" t="n">
         <v>40.9</v>
@@ -1819,19 +1886,19 @@
         <v>5.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA8" t="n">
         <v>23.7</v>
       </c>
       <c r="AB8" t="n">
-        <v>103.3</v>
+        <v>103.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE8" t="n">
         <v>6</v>
@@ -1846,22 +1913,22 @@
         <v>25</v>
       </c>
       <c r="AI8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AJ8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AM8" t="n">
         <v>18</v>
       </c>
       <c r="AN8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1876,13 +1943,13 @@
         <v>23</v>
       </c>
       <c r="AS8" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>28</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E9" t="n">
         <v>27</v>
       </c>
       <c r="F9" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>0.482</v>
+        <v>0.491</v>
       </c>
       <c r="H9" t="n">
         <v>48.4</v>
@@ -1953,7 +2020,7 @@
         <v>35.9</v>
       </c>
       <c r="J9" t="n">
-        <v>79.3</v>
+        <v>79.2</v>
       </c>
       <c r="K9" t="n">
         <v>0.453</v>
@@ -1965,19 +2032,19 @@
         <v>13.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.344</v>
+        <v>0.342</v>
       </c>
       <c r="O9" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="P9" t="n">
-        <v>22.3</v>
+        <v>22.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.745</v>
+        <v>0.744</v>
       </c>
       <c r="R9" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S9" t="n">
         <v>29.9</v>
@@ -1989,13 +2056,13 @@
         <v>20.2</v>
       </c>
       <c r="V9" t="n">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="W9" t="n">
         <v>6.3</v>
       </c>
       <c r="X9" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y9" t="n">
         <v>4</v>
@@ -2007,43 +2074,43 @@
         <v>19.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>93</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC9" t="n">
         <v>-1.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AH9" t="n">
         <v>12</v>
       </c>
       <c r="AI9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AJ9" t="n">
         <v>20</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM9" t="n">
         <v>28</v>
       </c>
       <c r="AN9" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO9" t="n">
         <v>29</v>
@@ -2055,7 +2122,7 @@
         <v>26</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS9" t="n">
         <v>16</v>
@@ -2064,7 +2131,7 @@
         <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="n">
         <v>1</v>
@@ -2073,22 +2140,22 @@
         <v>28</v>
       </c>
       <c r="AX9" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AY9" t="n">
         <v>6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
         <v>29</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2207,7 +2274,7 @@
         <v>24</v>
       </c>
       <c r="AH10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI10" t="n">
         <v>3</v>
@@ -2225,7 +2292,7 @@
         <v>17</v>
       </c>
       <c r="AN10" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
         <v>2</v>
@@ -2246,7 +2313,7 @@
         <v>12</v>
       </c>
       <c r="AU10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>3.6</v>
       </c>
       <c r="AD11" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2389,25 +2456,25 @@
         <v>7</v>
       </c>
       <c r="AH11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
         <v>6</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO11" t="n">
         <v>11</v>
@@ -2419,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
@@ -2428,19 +2495,19 @@
         <v>5</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV11" t="n">
         <v>14</v>
       </c>
       <c r="AW11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AZ11" t="n">
         <v>2</v>
@@ -2449,7 +2516,7 @@
         <v>17</v>
       </c>
       <c r="BB11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BC11" t="n">
         <v>7</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F12" t="n">
         <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>0.417</v>
+        <v>0.407</v>
       </c>
       <c r="H12" t="n">
         <v>48.5</v>
@@ -2499,28 +2566,28 @@
         <v>38.9</v>
       </c>
       <c r="J12" t="n">
-        <v>86.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="M12" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="N12" t="n">
-        <v>0.373</v>
+        <v>0.371</v>
       </c>
       <c r="O12" t="n">
         <v>19.2</v>
       </c>
       <c r="P12" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.805</v>
+        <v>0.804</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
@@ -2532,16 +2599,16 @@
         <v>43.6</v>
       </c>
       <c r="U12" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W12" t="n">
         <v>6.9</v>
       </c>
       <c r="X12" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y12" t="n">
         <v>5.5</v>
@@ -2556,13 +2623,13 @@
         <v>104.8</v>
       </c>
       <c r="AC12" t="n">
-        <v>-1.9</v>
+        <v>-2</v>
       </c>
       <c r="AD12" t="n">
         <v>1</v>
       </c>
       <c r="AE12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF12" t="n">
         <v>21</v>
@@ -2589,10 +2656,10 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
         <v>21</v>
@@ -2610,16 +2677,16 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV12" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AW12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AX12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2634,7 +2701,7 @@
         <v>5</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F13" t="n">
         <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>0.259</v>
+        <v>0.246</v>
       </c>
       <c r="H13" t="n">
         <v>48.6</v>
@@ -2690,19 +2757,19 @@
         <v>6.4</v>
       </c>
       <c r="M13" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.347</v>
+        <v>0.35</v>
       </c>
       <c r="O13" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P13" t="n">
         <v>22.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R13" t="n">
         <v>11.3</v>
@@ -2714,10 +2781,10 @@
         <v>40.2</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
@@ -2732,19 +2799,19 @@
         <v>20.9</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB13" t="n">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="AC13" t="n">
-        <v>-8.300000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE13" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF13" t="n">
         <v>27</v>
@@ -2753,10 +2820,10 @@
         <v>27</v>
       </c>
       <c r="AH13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2765,13 +2832,13 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AM13" t="n">
         <v>14</v>
       </c>
       <c r="AN13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO13" t="n">
         <v>27</v>
@@ -2795,7 +2862,7 @@
         <v>13</v>
       </c>
       <c r="AV13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>18</v>
@@ -2810,7 +2877,7 @@
         <v>16</v>
       </c>
       <c r="BA13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
         <v>26</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -2845,25 +2912,25 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F14" t="n">
         <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.821</v>
+        <v>0.825</v>
       </c>
       <c r="H14" t="n">
         <v>48.4</v>
       </c>
       <c r="I14" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="J14" t="n">
-        <v>85.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K14" t="n">
         <v>0.479</v>
@@ -2872,31 +2939,31 @@
         <v>6.9</v>
       </c>
       <c r="M14" t="n">
-        <v>18.9</v>
+        <v>18.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.368</v>
+        <v>0.371</v>
       </c>
       <c r="O14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="P14" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.768</v>
+        <v>0.769</v>
       </c>
       <c r="R14" t="n">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>44.3</v>
+        <v>44.4</v>
       </c>
       <c r="U14" t="n">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
         <v>13.6</v>
@@ -2905,7 +2972,7 @@
         <v>8.4</v>
       </c>
       <c r="X14" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y14" t="n">
         <v>4.5</v>
@@ -2914,16 +2981,16 @@
         <v>20.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB14" t="n">
-        <v>109.1</v>
+        <v>108.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="AE14" t="n">
         <v>1</v>
@@ -2935,7 +3002,7 @@
         <v>1</v>
       </c>
       <c r="AH14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI14" t="n">
         <v>1</v>
@@ -2944,7 +3011,7 @@
         <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,22 +3020,22 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP14" t="n">
         <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR14" t="n">
         <v>3</v>
       </c>
       <c r="AS14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT14" t="n">
         <v>1</v>
@@ -2983,13 +3050,13 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY14" t="n">
         <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -3027,34 +3094,34 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E15" t="n">
         <v>15</v>
       </c>
       <c r="F15" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>0.263</v>
+        <v>0.268</v>
       </c>
       <c r="H15" t="n">
         <v>48.4</v>
       </c>
       <c r="I15" t="n">
-        <v>34.7</v>
+        <v>34.6</v>
       </c>
       <c r="J15" t="n">
         <v>77.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L15" t="n">
         <v>4.6</v>
       </c>
       <c r="M15" t="n">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="N15" t="n">
         <v>0.333</v>
@@ -3066,22 +3133,22 @@
         <v>25.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R15" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S15" t="n">
         <v>28.6</v>
       </c>
       <c r="T15" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="U15" t="n">
         <v>16.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W15" t="n">
         <v>7.6</v>
@@ -3090,22 +3157,22 @@
         <v>4.4</v>
       </c>
       <c r="Y15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z15" t="n">
         <v>22.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>93.3</v>
+        <v>93.2</v>
       </c>
       <c r="AC15" t="n">
         <v>-6.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3129,7 +3196,7 @@
         <v>23</v>
       </c>
       <c r="AL15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AM15" t="n">
         <v>27</v>
@@ -3147,7 +3214,7 @@
         <v>23</v>
       </c>
       <c r="AR15" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS15" t="n">
         <v>27</v>
@@ -3162,13 +3229,13 @@
         <v>23</v>
       </c>
       <c r="AW15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ15" t="n">
         <v>21</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE16" t="n">
         <v>14</v>
@@ -3308,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AL16" t="n">
         <v>12</v>
@@ -3323,13 +3390,13 @@
         <v>28</v>
       </c>
       <c r="AP16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ16" t="n">
         <v>24</v>
       </c>
       <c r="AR16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS16" t="n">
         <v>23</v>
@@ -3338,7 +3405,7 @@
         <v>28</v>
       </c>
       <c r="AU16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -3409,16 +3476,16 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.5</v>
+        <v>81.3</v>
       </c>
       <c r="K17" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L17" t="n">
         <v>5.9</v>
       </c>
       <c r="M17" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="N17" t="n">
         <v>0.363</v>
@@ -3427,34 +3494,34 @@
         <v>20.6</v>
       </c>
       <c r="P17" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q17" t="n">
         <v>0.78</v>
       </c>
       <c r="R17" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="S17" t="n">
         <v>28.9</v>
       </c>
       <c r="T17" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U17" t="n">
         <v>21.6</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X17" t="n">
         <v>3.7</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z17" t="n">
         <v>24</v>
@@ -3463,13 +3530,13 @@
         <v>23.3</v>
       </c>
       <c r="AB17" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>15</v>
@@ -3487,10 +3554,10 @@
         <v>16</v>
       </c>
       <c r="AJ17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK17" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="n">
         <v>23</v>
@@ -3499,7 +3566,7 @@
         <v>21</v>
       </c>
       <c r="AN17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AO17" t="n">
         <v>7</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G18" t="n">
-        <v>0.316</v>
+        <v>0.321</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3594,25 +3661,25 @@
         <v>83.8</v>
       </c>
       <c r="K18" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L18" t="n">
-        <v>6.2</v>
+        <v>6.3</v>
       </c>
       <c r="M18" t="n">
         <v>18.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.342</v>
+        <v>0.345</v>
       </c>
       <c r="O18" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P18" t="n">
         <v>24.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R18" t="n">
         <v>12.3</v>
@@ -3621,7 +3688,7 @@
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>42</v>
+        <v>42.1</v>
       </c>
       <c r="U18" t="n">
         <v>20.6</v>
@@ -3639,19 +3706,19 @@
         <v>6.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="AA18" t="n">
         <v>20.5</v>
       </c>
       <c r="AB18" t="n">
-        <v>99.59999999999999</v>
+        <v>99.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>-4</v>
+        <v>-3.8</v>
       </c>
       <c r="AD18" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE18" t="n">
         <v>25</v>
@@ -3666,7 +3733,7 @@
         <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ18" t="n">
         <v>5</v>
@@ -3681,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="AN18" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AO18" t="n">
         <v>17</v>
@@ -3690,7 +3757,7 @@
         <v>14</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>4</v>
@@ -3708,10 +3775,10 @@
         <v>16</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3720,7 +3787,7 @@
         <v>19</v>
       </c>
       <c r="BA18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB18" t="n">
         <v>14</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -3755,25 +3822,25 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E19" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F19" t="n">
         <v>32</v>
       </c>
       <c r="G19" t="n">
-        <v>0.448</v>
+        <v>0.439</v>
       </c>
       <c r="H19" t="n">
         <v>48.5</v>
       </c>
       <c r="I19" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J19" t="n">
-        <v>80.3</v>
+        <v>80.2</v>
       </c>
       <c r="K19" t="n">
         <v>0.443</v>
@@ -3782,34 +3849,34 @@
         <v>7.8</v>
       </c>
       <c r="M19" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N19" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O19" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="P19" t="n">
         <v>24.7</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.779</v>
+        <v>0.776</v>
       </c>
       <c r="R19" t="n">
         <v>11.1</v>
       </c>
       <c r="S19" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T19" t="n">
-        <v>40.5</v>
+        <v>40.4</v>
       </c>
       <c r="U19" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V19" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="W19" t="n">
         <v>6.9</v>
@@ -3821,34 +3888,34 @@
         <v>5</v>
       </c>
       <c r="Z19" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA19" t="n">
         <v>20.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>98.2</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.4</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH19" t="n">
         <v>7</v>
       </c>
       <c r="AI19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ19" t="n">
         <v>15</v>
@@ -3863,22 +3930,22 @@
         <v>7</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AS19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
         <v>21</v>
@@ -3887,10 +3954,10 @@
         <v>28</v>
       </c>
       <c r="AV19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX19" t="n">
         <v>20</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E20" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F20" t="n">
         <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>0.607</v>
+        <v>0.6</v>
       </c>
       <c r="H20" t="n">
         <v>48.1</v>
@@ -3961,13 +4028,13 @@
         <v>0.456</v>
       </c>
       <c r="L20" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M20" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O20" t="n">
         <v>18.7</v>
@@ -3976,25 +4043,25 @@
         <v>23.1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.8080000000000001</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="R20" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="S20" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T20" t="n">
-        <v>39.1</v>
+        <v>38.8</v>
       </c>
       <c r="U20" t="n">
         <v>19.8</v>
       </c>
       <c r="V20" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W20" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X20" t="n">
         <v>4.3</v>
@@ -4003,19 +4070,19 @@
         <v>3.6</v>
       </c>
       <c r="Z20" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB20" t="n">
-        <v>96.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="AC20" t="n">
         <v>2.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE20" t="n">
         <v>10</v>
@@ -4036,7 +4103,7 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4048,7 +4115,7 @@
         <v>6</v>
       </c>
       <c r="AO20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP20" t="n">
         <v>22</v>
@@ -4072,7 +4139,7 @@
         <v>4</v>
       </c>
       <c r="AW20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX20" t="n">
         <v>23</v>
@@ -4084,10 +4151,10 @@
         <v>15</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BB20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BC20" t="n">
         <v>10</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E21" t="n">
         <v>24</v>
       </c>
       <c r="F21" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G21" t="n">
-        <v>0.421</v>
+        <v>0.429</v>
       </c>
       <c r="H21" t="n">
         <v>48.3</v>
@@ -4137,19 +4204,19 @@
         <v>38.7</v>
       </c>
       <c r="J21" t="n">
-        <v>87.2</v>
+        <v>87</v>
       </c>
       <c r="K21" t="n">
-        <v>0.444</v>
+        <v>0.445</v>
       </c>
       <c r="L21" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="M21" t="n">
         <v>28.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.362</v>
+        <v>0.36</v>
       </c>
       <c r="O21" t="n">
         <v>18</v>
@@ -4161,22 +4228,22 @@
         <v>0.793</v>
       </c>
       <c r="R21" t="n">
-        <v>11.1</v>
+        <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>31.7</v>
+        <v>31.8</v>
       </c>
       <c r="T21" t="n">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="U21" t="n">
         <v>21.7</v>
       </c>
       <c r="V21" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W21" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X21" t="n">
         <v>2.3</v>
@@ -4185,31 +4252,31 @@
         <v>5.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="AA21" t="n">
         <v>19.3</v>
       </c>
       <c r="AB21" t="n">
-        <v>105.9</v>
+        <v>105.8</v>
       </c>
       <c r="AC21" t="n">
         <v>-2</v>
       </c>
       <c r="AD21" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AG21" t="n">
         <v>20</v>
       </c>
       <c r="AH21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AI21" t="n">
         <v>5</v>
@@ -4218,10 +4285,10 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM21" t="n">
         <v>1</v>
@@ -4230,22 +4297,22 @@
         <v>20</v>
       </c>
       <c r="AO21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AP21" t="n">
         <v>24</v>
       </c>
       <c r="AQ21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU21" t="n">
         <v>9</v>
@@ -4263,7 +4330,7 @@
         <v>23</v>
       </c>
       <c r="AZ21" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4272,7 +4339,7 @@
         <v>4</v>
       </c>
       <c r="BC21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -4379,37 +4446,37 @@
         <v>-6.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>28</v>
       </c>
       <c r="AF22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ22" t="n">
         <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL22" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AM22" t="n">
         <v>30</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
@@ -4418,7 +4485,7 @@
         <v>9</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR22" t="n">
         <v>5</v>
@@ -4448,7 +4515,7 @@
         <v>14</v>
       </c>
       <c r="BA22" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB22" t="n">
         <v>19</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -4483,16 +4550,16 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F23" t="n">
         <v>15</v>
       </c>
       <c r="G23" t="n">
-        <v>0.737</v>
+        <v>0.732</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
@@ -4501,40 +4568,40 @@
         <v>36</v>
       </c>
       <c r="J23" t="n">
-        <v>78.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.46</v>
+        <v>0.459</v>
       </c>
       <c r="L23" t="n">
         <v>10.5</v>
       </c>
       <c r="M23" t="n">
-        <v>26.5</v>
+        <v>26.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0.394</v>
+        <v>0.396</v>
       </c>
       <c r="O23" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="P23" t="n">
-        <v>27.5</v>
+        <v>27.3</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="S23" t="n">
         <v>33.2</v>
       </c>
       <c r="T23" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U23" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="V23" t="n">
         <v>14.2</v>
@@ -4546,22 +4613,22 @@
         <v>5.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z23" t="n">
         <v>20.3</v>
       </c>
       <c r="AA23" t="n">
-        <v>22.6</v>
+        <v>22.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>102.4</v>
+        <v>102.2</v>
       </c>
       <c r="AC23" t="n">
         <v>7.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,13 +4640,13 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ23" t="n">
         <v>24</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>21</v>
-      </c>
-      <c r="AJ23" t="n">
-        <v>25</v>
       </c>
       <c r="AK23" t="n">
         <v>9</v>
@@ -4597,13 +4664,13 @@
         <v>10</v>
       </c>
       <c r="AP23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
         <v>1</v>
@@ -4618,7 +4685,7 @@
         <v>13</v>
       </c>
       <c r="AW23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -4665,16 +4732,16 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" t="n">
         <v>28</v>
       </c>
       <c r="G24" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="H24" t="n">
         <v>48.1</v>
@@ -4683,10 +4750,10 @@
         <v>36.5</v>
       </c>
       <c r="J24" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.454</v>
+        <v>0.453</v>
       </c>
       <c r="L24" t="n">
         <v>4.2</v>
@@ -4695,34 +4762,34 @@
         <v>13.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0.317</v>
+        <v>0.315</v>
       </c>
       <c r="O24" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P24" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="R24" t="n">
         <v>12.9</v>
       </c>
       <c r="S24" t="n">
-        <v>29.7</v>
+        <v>29.8</v>
       </c>
       <c r="T24" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U24" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V24" t="n">
         <v>14.9</v>
       </c>
       <c r="W24" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X24" t="n">
         <v>5.4</v>
@@ -4737,16 +4804,16 @@
         <v>21.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="AC24" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AF24" t="n">
         <v>15</v>
@@ -4755,7 +4822,7 @@
         <v>15</v>
       </c>
       <c r="AH24" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
@@ -4764,10 +4831,10 @@
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AL24" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP24" t="n">
         <v>11</v>
@@ -4794,13 +4861,13 @@
         <v>9</v>
       </c>
       <c r="AU24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV24" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AX24" t="n">
         <v>8</v>
@@ -4809,13 +4876,13 @@
         <v>16</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BA24" t="n">
         <v>11</v>
       </c>
       <c r="BB24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC24" t="n">
         <v>14</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -4925,7 +4992,7 @@
         <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE25" t="n">
         <v>12</v>
@@ -4949,25 +5016,25 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
         <v>4</v>
       </c>
       <c r="AP25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR25" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS25" t="n">
         <v>9</v>
@@ -4982,7 +5049,7 @@
         <v>29</v>
       </c>
       <c r="AW25" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -5044,70 +5111,70 @@
         <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="J26" t="n">
         <v>79.3</v>
       </c>
       <c r="K26" t="n">
-        <v>0.464</v>
+        <v>0.463</v>
       </c>
       <c r="L26" t="n">
         <v>7.3</v>
       </c>
       <c r="M26" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="N26" t="n">
-        <v>0.379</v>
+        <v>0.382</v>
       </c>
       <c r="O26" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P26" t="n">
-        <v>24.3</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.763</v>
+        <v>0.759</v>
       </c>
       <c r="R26" t="n">
         <v>13.1</v>
       </c>
       <c r="S26" t="n">
-        <v>28.2</v>
+        <v>28.3</v>
       </c>
       <c r="T26" t="n">
         <v>41.3</v>
       </c>
       <c r="U26" t="n">
-        <v>20.5</v>
+        <v>20.6</v>
       </c>
       <c r="V26" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="W26" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X26" t="n">
         <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AA26" t="n">
         <v>21</v>
       </c>
       <c r="AB26" t="n">
-        <v>99.3</v>
+        <v>99.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
@@ -5119,7 +5186,7 @@
         <v>8</v>
       </c>
       <c r="AH26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI26" t="n">
         <v>15</v>
@@ -5137,16 +5204,16 @@
         <v>12</v>
       </c>
       <c r="AN26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AQ26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,31 +5225,31 @@
         <v>15</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AV26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW26" t="n">
         <v>25</v>
       </c>
       <c r="AX26" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AY26" t="n">
         <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA26" t="n">
         <v>14</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E27" t="n">
         <v>12</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>0.203</v>
+        <v>0.207</v>
       </c>
       <c r="H27" t="n">
         <v>48.6</v>
       </c>
       <c r="I27" t="n">
-        <v>36</v>
+        <v>36.1</v>
       </c>
       <c r="J27" t="n">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>0.445</v>
+        <v>0.446</v>
       </c>
       <c r="L27" t="n">
         <v>6.6</v>
@@ -5241,13 +5308,13 @@
         <v>18.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0.356</v>
+        <v>0.357</v>
       </c>
       <c r="O27" t="n">
         <v>20.7</v>
       </c>
       <c r="P27" t="n">
-        <v>25.8</v>
+        <v>25.7</v>
       </c>
       <c r="Q27" t="n">
         <v>0.803</v>
@@ -5259,10 +5326,10 @@
         <v>28.5</v>
       </c>
       <c r="T27" t="n">
-        <v>38.5</v>
+        <v>38.4</v>
       </c>
       <c r="U27" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="V27" t="n">
         <v>15.8</v>
@@ -5271,7 +5338,7 @@
         <v>6.9</v>
       </c>
       <c r="X27" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.2</v>
@@ -5283,13 +5350,13 @@
         <v>21.7</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>-9.5</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>30</v>
@@ -5304,16 +5371,16 @@
         <v>6</v>
       </c>
       <c r="AI27" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM27" t="n">
         <v>15</v>
@@ -5322,7 +5389,7 @@
         <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP27" t="n">
         <v>12</v>
@@ -5331,7 +5398,7 @@
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS27" t="n">
         <v>28</v>
@@ -5340,13 +5407,13 @@
         <v>30</v>
       </c>
       <c r="AU27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV27" t="n">
         <v>26</v>
       </c>
       <c r="AW27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AX27" t="n">
         <v>27</v>
@@ -5361,7 +5428,7 @@
         <v>10</v>
       </c>
       <c r="BB27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -5393,28 +5460,28 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E28" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.696</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J28" t="n">
         <v>79.7</v>
       </c>
       <c r="K28" t="n">
-        <v>0.465</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
         <v>8</v>
@@ -5423,19 +5490,19 @@
         <v>20.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.394</v>
+        <v>0.393</v>
       </c>
       <c r="O28" t="n">
-        <v>15.5</v>
+        <v>15.7</v>
       </c>
       <c r="P28" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.771</v>
       </c>
       <c r="R28" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S28" t="n">
         <v>32.2</v>
@@ -5444,10 +5511,10 @@
         <v>40.9</v>
       </c>
       <c r="U28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V28" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W28" t="n">
         <v>5.8</v>
@@ -5456,22 +5523,22 @@
         <v>4.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB28" t="n">
         <v>97.59999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5495,7 +5562,7 @@
         <v>7</v>
       </c>
       <c r="AL28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
@@ -5510,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR28" t="n">
         <v>29</v>
@@ -5519,7 +5586,7 @@
         <v>4</v>
       </c>
       <c r="AT28" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU28" t="n">
         <v>7</v>
@@ -5546,7 +5613,7 @@
         <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-3.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE29" t="n">
         <v>22</v>
@@ -5662,7 +5729,7 @@
         <v>23</v>
       </c>
       <c r="AG29" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>22</v>
@@ -5686,7 +5753,7 @@
         <v>11</v>
       </c>
       <c r="AO29" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP29" t="n">
         <v>27</v>
@@ -5722,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB29" t="n">
         <v>22</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
         <v>23</v>
       </c>
       <c r="G30" t="n">
-        <v>0.603</v>
+        <v>0.596</v>
       </c>
       <c r="H30" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I30" t="n">
-        <v>38.2</v>
+        <v>38.1</v>
       </c>
       <c r="J30" t="n">
         <v>79.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -5787,34 +5854,34 @@
         <v>14</v>
       </c>
       <c r="N30" t="n">
-        <v>0.345</v>
+        <v>0.344</v>
       </c>
       <c r="O30" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="P30" t="n">
-        <v>28.2</v>
+        <v>28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.772</v>
+        <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.7</v>
       </c>
       <c r="S30" t="n">
         <v>29.2</v>
       </c>
       <c r="T30" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U30" t="n">
-        <v>24.6</v>
+        <v>24.5</v>
       </c>
       <c r="V30" t="n">
         <v>14.9</v>
       </c>
       <c r="W30" t="n">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="X30" t="n">
         <v>4.8</v>
@@ -5829,16 +5896,16 @@
         <v>23.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>103</v>
+        <v>102.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>10</v>
@@ -5847,16 +5914,16 @@
         <v>10</v>
       </c>
       <c r="AH30" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI30" t="n">
         <v>6</v>
       </c>
       <c r="AJ30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL30" t="n">
         <v>26</v>
@@ -5865,7 +5932,7 @@
         <v>26</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,7 +5941,7 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR30" t="n">
         <v>10</v>
@@ -5889,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>15</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
@@ -5939,22 +6006,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E31" t="n">
         <v>13</v>
       </c>
       <c r="F31" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G31" t="n">
-        <v>0.228</v>
+        <v>0.232</v>
       </c>
       <c r="H31" t="n">
         <v>48.1</v>
       </c>
       <c r="I31" t="n">
-        <v>36.2</v>
+        <v>36.1</v>
       </c>
       <c r="J31" t="n">
         <v>81.40000000000001</v>
@@ -5969,16 +6036,16 @@
         <v>15.5</v>
       </c>
       <c r="N31" t="n">
-        <v>0.324</v>
+        <v>0.323</v>
       </c>
       <c r="O31" t="n">
         <v>17.2</v>
       </c>
       <c r="P31" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R31" t="n">
         <v>11.8</v>
@@ -5987,16 +6054,16 @@
         <v>28.1</v>
       </c>
       <c r="T31" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="U31" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V31" t="n">
-        <v>14</v>
+        <v>13.9</v>
       </c>
       <c r="W31" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="X31" t="n">
         <v>4.1</v>
@@ -6011,19 +6078,19 @@
         <v>19.4</v>
       </c>
       <c r="AB31" t="n">
-        <v>94.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="AC31" t="n">
         <v>-7.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="AE31" t="n">
         <v>28</v>
       </c>
       <c r="AF31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG31" t="n">
         <v>28</v>
@@ -6035,10 +6102,10 @@
         <v>20</v>
       </c>
       <c r="AJ31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AK31" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AL31" t="n">
         <v>25</v>
@@ -6053,10 +6120,10 @@
         <v>26</v>
       </c>
       <c r="AP31" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AQ31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR31" t="n">
         <v>8</v>
@@ -6065,19 +6132,19 @@
         <v>30</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AU31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV31" t="n">
         <v>12</v>
       </c>
       <c r="AW31" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AX31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-25-2008-09</t>
+          <t>2009-02-25</t>
         </is>
       </c>
     </row>
